--- a/TableofProjects.xlsx
+++ b/TableofProjects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/30004fd22ebf6418/Desktop/Data Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F6E6853-9B09-4D40-B4C3-00FAC5C10BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{7F6E6853-9B09-4D40-B4C3-00FAC5C10BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A232827D-A69E-4B37-9F8B-17ADB9921A89}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{219F9499-B288-49CD-86F1-8625D0232252}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$E$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>Project Descriptions as of 3/30/2026</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t xml:space="preserve">Illustration of R skills using Palmer Penguins data set </t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>BGG Project</t>
   </si>
 </sst>
 </file>
@@ -125,7 +131,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,6 +143,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -180,10 +194,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -198,8 +213,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -532,140 +549,160 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7762B3B-2E3E-4A92-AD79-6C8207D23CAA}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" customWidth="1"/>
-    <col min="4" max="4" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" customWidth="1"/>
+    <col min="3" max="3" width="86.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" customWidth="1"/>
+    <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4">
+      <c r="D4" s="4">
         <v>45809</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4">
+      <c r="D5" s="4">
         <v>45901</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4">
+      <c r="D7" s="4">
         <v>46107</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4">
+      <c r="D8" s="4">
         <v>46107</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4">
+      <c r="D9" s="4">
         <v>46107</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="9"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="9"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D13" s="9"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{87F0332D-E118-412E-B99C-50F14E9E2A59}"/>
+    <hyperlink ref="B9" r:id="rId2" xr:uid="{C5131CA9-5584-47EB-BC12-34F3D9FA18A7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>